--- a/Reference/バーコード現品票20260402/ボディー　バーコード一覧.xlsx
+++ b/Reference/バーコード現品票20260402/ボディー　バーコード一覧.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER101\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.10.13\愛知public\★製造部関連フォルダー\4工場\芳賀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D75E36E3-F72B-43EF-911A-E977FE9FB698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCECDD18-C2CC-4515-845E-D70CD3A202BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{4A0C8197-23CB-4D59-8779-3CDAF6BEF46B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A0C8197-23CB-4D59-8779-3CDAF6BEF46B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,12 +37,164 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+  <si>
+    <t>川路　弘規</t>
+    <rPh sb="0" eb="2">
+      <t>カワジ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白鳥　大亮</t>
+    <rPh sb="0" eb="2">
+      <t>シラトリ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ダイスケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新美　達也</t>
+    <rPh sb="0" eb="2">
+      <t>ニイミ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>タツヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&gt; トピック: データ収集打合せ</t>
+  </si>
+  <si>
+    <t>&gt; 時刻: 2026年3月30日 13:30 大阪、札幌、東京</t>
+  </si>
+  <si>
+    <t>&gt; Zoom ミーティングに参加する</t>
+  </si>
+  <si>
+    <t>&gt; https://us02web.zoom.us/j/84397295863?pwd=wPw3Sxe8ZFtiGce4KK6e4un5mN2W</t>
+  </si>
+  <si>
+    <t>&gt; 12.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt; </t>
+  </si>
+  <si>
+    <t>&gt; ミーティング ID: 843 9729 5863</t>
+  </si>
+  <si>
+    <t>&gt; パスコード: 269748</t>
+  </si>
+  <si>
+    <t>坪内　まこと</t>
+    <rPh sb="0" eb="2">
+      <t>ツボウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平野　雅之</t>
+    <rPh sb="0" eb="2">
+      <t>ヒラノ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>マサユキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジョド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白井　祐樹</t>
+    <rPh sb="0" eb="2">
+      <t>シライ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ユウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大竹　由香利</t>
+    <rPh sb="0" eb="2">
+      <t>オオタケ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ユカリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>兼次　南帆</t>
+    <rPh sb="0" eb="2">
+      <t>カネシ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ナホ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白井　博敏</t>
+    <rPh sb="0" eb="2">
+      <t>シライ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒロトシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>永井　なつみ</t>
+    <rPh sb="0" eb="2">
+      <t>ナガイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I4ボディ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I4Hボディ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>従業員バーコード</t>
+    <rPh sb="0" eb="3">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>氏名</t>
+    <rPh sb="0" eb="2">
+      <t>シメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -57,16 +210,52 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="BIZ UDゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -74,21 +263,118 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -109,15 +395,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:colOff>32302</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>31472</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2009775</xdr:colOff>
+      <xdr:colOff>2030302</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>685800</xdr:rowOff>
+      <xdr:rowOff>643472</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -129,7 +415,7 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -147,8 +433,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="704850" y="352425"/>
-          <a:ext cx="1990725" cy="571500"/>
+          <a:off x="719759" y="768624"/>
+          <a:ext cx="1998000" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -170,15 +456,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
+      <xdr:colOff>32302</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>31627</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2030302</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>657225</xdr:rowOff>
+      <xdr:rowOff>643627</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -190,7 +476,7 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -208,8 +494,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="742950" y="1085850"/>
-          <a:ext cx="1990725" cy="571500"/>
+          <a:off x="719759" y="1439670"/>
+          <a:ext cx="1998000" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -231,15 +517,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
+      <xdr:colOff>32302</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>31781</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2019300</xdr:colOff>
+      <xdr:colOff>2030302</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>714375</xdr:rowOff>
+      <xdr:rowOff>643781</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -251,7 +537,7 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -269,8 +555,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="714375" y="1905000"/>
-          <a:ext cx="1990725" cy="571500"/>
+          <a:off x="719759" y="2110716"/>
+          <a:ext cx="1998000" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -292,15 +578,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:colOff>32302</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>31936</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2009775</xdr:colOff>
+      <xdr:colOff>2030302</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>666750</xdr:rowOff>
+      <xdr:rowOff>643936</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -312,7 +598,7 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -330,8 +616,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="704850" y="2619375"/>
-          <a:ext cx="1990725" cy="571500"/>
+          <a:off x="719759" y="2781762"/>
+          <a:ext cx="1998000" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -353,15 +639,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
+      <xdr:colOff>32302</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>32091</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2030302</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>714375</xdr:rowOff>
+      <xdr:rowOff>644091</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -373,7 +659,7 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -391,8 +677,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="742950" y="3429000"/>
-          <a:ext cx="1990725" cy="571500"/>
+          <a:off x="719759" y="3452808"/>
+          <a:ext cx="1998000" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -414,15 +700,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:colOff>32302</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>32245</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2028825</xdr:colOff>
+      <xdr:colOff>2030302</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>685800</xdr:rowOff>
+      <xdr:rowOff>644245</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -434,7 +720,7 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -452,8 +738,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="723900" y="4162425"/>
-          <a:ext cx="1990725" cy="571500"/>
+          <a:off x="719759" y="4123854"/>
+          <a:ext cx="1998000" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -475,15 +761,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:colOff>32302</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>32400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2000250</xdr:colOff>
+      <xdr:colOff>2030302</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>742950</xdr:rowOff>
+      <xdr:rowOff>644400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -495,7 +781,7 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -513,8 +799,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="695325" y="4981575"/>
-          <a:ext cx="1990725" cy="571500"/>
+          <a:off x="719759" y="4794900"/>
+          <a:ext cx="1998000" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -536,15 +822,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:colOff>32302</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>32712</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2038350</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>695325</xdr:rowOff>
+      <xdr:colOff>2030302</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>644712</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -556,7 +842,7 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -574,8 +860,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="733425" y="5695950"/>
-          <a:ext cx="1990725" cy="571500"/>
+          <a:off x="719759" y="6136995"/>
+          <a:ext cx="1998000" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -597,15 +883,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:colOff>27333</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>31472</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2009775</xdr:colOff>
+      <xdr:colOff>2025333</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>714375</xdr:rowOff>
+      <xdr:rowOff>643472</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -617,7 +903,7 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -635,8 +921,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2752725" y="381000"/>
-          <a:ext cx="1990725" cy="571500"/>
+          <a:off x="2760594" y="768624"/>
+          <a:ext cx="1998000" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -658,15 +944,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
+      <xdr:colOff>27333</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>31627</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2019300</xdr:colOff>
+      <xdr:colOff>2025333</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>714375</xdr:rowOff>
+      <xdr:rowOff>643627</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -678,7 +964,7 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -696,8 +982,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2762250" y="1143000"/>
-          <a:ext cx="1990725" cy="571500"/>
+          <a:off x="2760594" y="1439670"/>
+          <a:ext cx="1998000" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -719,15 +1005,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:colOff>27333</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>31781</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2009775</xdr:colOff>
+      <xdr:colOff>2025333</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>704850</xdr:rowOff>
+      <xdr:rowOff>643781</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -739,7 +1025,7 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -757,8 +1043,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2752725" y="1895475"/>
-          <a:ext cx="1990725" cy="571500"/>
+          <a:off x="2760594" y="2110716"/>
+          <a:ext cx="1998000" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -780,15 +1066,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
+      <xdr:colOff>27333</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>31936</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2025333</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>695325</xdr:rowOff>
+      <xdr:rowOff>643936</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -800,7 +1086,7 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -818,8 +1104,735 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2790825" y="2647950"/>
-          <a:ext cx="1990725" cy="571500"/>
+          <a:off x="2760594" y="2781762"/>
+          <a:ext cx="1998000" cy="612000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>38050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>6375</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>650050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="図 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9ECD057-96D7-F63F-22B0-516D0E823919}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5953125" y="771475"/>
+          <a:ext cx="2340000" cy="612000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38218</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>6375</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>650218</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EF375E6-DC7B-E9A1-B6D2-03073FE8ABB2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5953125" y="1438393"/>
+          <a:ext cx="2340000" cy="612000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>38386</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>6375</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>650386</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A9E6AE0-1109-00F5-3754-63E141CC3C8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5953125" y="2105311"/>
+          <a:ext cx="2340000" cy="612000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>38554</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>6375</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>650554</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF3BE1B0-B423-C2D0-0028-1921854E187A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5953125" y="2772229"/>
+          <a:ext cx="2340000" cy="612000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>38722</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>6375</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>650722</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="図 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B829380E-FF43-F714-E676-93DE586B458C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5953125" y="3439147"/>
+          <a:ext cx="2340000" cy="612000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>38890</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>6375</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>650890</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="図 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4851A84A-55DD-AD84-5A01-82A753070326}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5953125" y="4106065"/>
+          <a:ext cx="2340000" cy="612000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>39058</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>6375</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>651058</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="図 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22B91792-F14C-DA72-FE98-8BC44C88EA4F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5953125" y="4772983"/>
+          <a:ext cx="2340000" cy="612000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>32302</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>32555</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1998000" cy="612000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="図 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5AD845B-9491-4682-8F49-1A923E7F241C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="719759" y="5465946"/>
+          <a:ext cx="1998000" cy="612000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>39226</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>6375</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>651226</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="図 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAC6386F-6D2E-53EC-DF2F-ACE11FF29B13}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5953125" y="5439901"/>
+          <a:ext cx="2340000" cy="612000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>39394</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>6375</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>651394</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="図 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{553E0193-5394-63A0-08A5-97C0EDC51C8D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5953125" y="6106819"/>
+          <a:ext cx="2340000" cy="612000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>39562</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>6375</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>651562</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="図 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E18F0DE0-8869-1B48-D0DC-DAB824D60BE2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5953125" y="6773737"/>
+          <a:ext cx="2340000" cy="612000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>39730</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>6375</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>651730</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="図 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E5F13D4-5EE2-EB21-EA19-93D5F82FECE8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5953125" y="7440655"/>
+          <a:ext cx="2340000" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1158,27 +2171,185 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{080F7178-1010-4FAC-A027-4F758614A9AB}">
-  <dimension ref="B2:B9"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="B1:F15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="3" width="26.875" customWidth="1"/>
+    <col min="1" max="1" width="9" style="4"/>
+    <col min="2" max="3" width="26.875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="14.875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="31.125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="12.625" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" ht="60" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="2:2" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="1"/>
+    <row r="1" spans="2:6" s="5" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="4" spans="2:2" ht="60" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="5" spans="2:2" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="1"/>
+    <row r="2" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="9" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="2:2" ht="60" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="7" spans="2:2" ht="60" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="8" spans="2:2" ht="60" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="2:2" ht="60" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="11"/>
+      <c r="C3" s="10"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="11"/>
+      <c r="C5" s="10"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E11" s="6"/>
+      <c r="F11" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E12" s="6"/>
+      <c r="F12" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E13" s="6"/>
+      <c r="F13" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="15" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC4B4F76-2616-4137-86C3-A7C14FDA778F}">
+  <dimension ref="C2:C10"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="2" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" display="https://us02web.zoom.us/j/84397295863?pwd=wPw3Sxe8ZFtiGce4KK6e4un5mN2W" xr:uid="{2744D626-2828-414E-8198-4EAAE1EE4E52}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Reference/バーコード現品票20260402/ボディー　バーコード一覧.xlsx
+++ b/Reference/バーコード現品票20260402/ボディー　バーコード一覧.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.10.13\愛知public\★製造部関連フォルダー\4工場\芳賀\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myProgram\GitHub\body_inspect_visualize_coba\Reference\バーコード現品票20260402\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCECDD18-C2CC-4515-845E-D70CD3A202BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B836245-D6A3-4A6B-B16D-815D8C746F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A0C8197-23CB-4D59-8779-3CDAF6BEF46B}"/>
   </bookViews>
@@ -241,7 +241,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -251,6 +251,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -335,7 +341,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -371,6 +377,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2171,7 +2180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{080F7178-1010-4FAC-A027-4F758614A9AB}">
-  <dimension ref="B1:F15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -2182,7 +2191,7 @@
     <col min="7" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="5" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" s="5" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B1" s="5" t="s">
         <v>20</v>
       </c>
@@ -2196,7 +2205,10 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
       <c r="E2" s="8"/>
@@ -2204,7 +2216,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
       <c r="B3" s="11"/>
       <c r="C3" s="10"/>
       <c r="E3" s="6"/>
@@ -2212,7 +2227,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="E4" s="6"/>
@@ -2220,7 +2238,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
       <c r="B5" s="11"/>
       <c r="C5" s="10"/>
       <c r="E5" s="6"/>
@@ -2228,7 +2249,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="E6" s="6"/>
@@ -2236,7 +2260,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="12">
+        <v>6</v>
+      </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="E7" s="6"/>
@@ -2244,7 +2271,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="E8" s="6"/>
@@ -2252,7 +2282,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="12">
+        <v>8</v>
+      </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="E9" s="6"/>
@@ -2260,7 +2293,10 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="E10" s="6"/>
@@ -2268,26 +2304,26 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E11" s="6"/>
       <c r="F11" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E12" s="6"/>
       <c r="F12" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E13" s="6"/>
       <c r="F13" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="15" spans="2:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="15" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Reference/バーコード現品票20260402/ボディー　バーコード一覧.xlsx
+++ b/Reference/バーコード現品票20260402/ボディー　バーコード一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myProgram\GitHub\body_inspect_visualize_coba\Reference\バーコード現品票20260402\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B836245-D6A3-4A6B-B16D-815D8C746F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA5BE2C-0DE0-4AE1-AA07-47C04BF7B507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A0C8197-23CB-4D59-8779-3CDAF6BEF46B}"/>
   </bookViews>
@@ -241,7 +241,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -251,12 +251,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -378,7 +372,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -831,15 +825,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>32302</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>32712</xdr:rowOff>
+      <xdr:colOff>24020</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>40994</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2030302</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>644712</xdr:rowOff>
+      <xdr:colOff>2022020</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>652994</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -869,7 +863,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="719759" y="6136995"/>
+          <a:off x="711477" y="5474385"/>
           <a:ext cx="1998000" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1560,62 +1554,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>32302</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>32555</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1998000" cy="612000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="図 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5AD845B-9491-4682-8F49-1A923E7F241C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="719759" y="5465946"/>
-          <a:ext cx="1998000" cy="612000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -2272,7 +2210,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="4">
+      <c r="A8" s="12">
         <v>7</v>
       </c>
       <c r="B8" s="10"/>
